--- a/questionnaire_templates/005_gender_transition_support_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/005_gender_transition_support_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1003,8 +1003,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'non-binary'}</t>
+          <t>non-binary</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Binary'}</t>
+          <t>Non-Binary</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'trans_female'}</t>
+          <t>trans_female</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Trans Female'}</t>
+          <t>Trans Female</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'trans_male'}</t>
+          <t>trans_male</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Trans Male'}</t>
+          <t>Trans Male</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'not_applicable'}</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'counseling/therapy'}</t>
+          <t>counseling/therapy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Counseling/Therapy'}</t>
+          <t>Counseling/Therapy</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'medical'}</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Medical'}</t>
+          <t>Medical</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'support_groups'}</t>
+          <t>support_groups</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Support Groups'}</t>
+          <t>Support Groups</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'very_unsatisfactory'}</t>
+          <t>very_unsatisfactory</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Very Unsatisfactory'}</t>
+          <t>Very Unsatisfactory</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'unsatisfactory'}</t>
+          <t>unsatisfactory</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Unsatisfactory'}</t>
+          <t>Unsatisfactory</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'satisfactory'}</t>
+          <t>satisfactory</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfactory'}</t>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfactory'}</t>
+          <t>very_satisfactory</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfactory'}</t>
+          <t>Very Satisfactory</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'unsatisfactory'}</t>
+          <t>unsatisfactory</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Unsatisfactory'}</t>
+          <t>Unsatisfactory</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'satisfactory'}</t>
+          <t>satisfactory</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfactory'}</t>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfactory'}</t>
+          <t>very_satisfactory</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfactory'}</t>
+          <t>Very Satisfactory</t>
         </is>
       </c>
     </row>
